--- a/public/templates/planora_import_template.xlsx
+++ b/public/templates/planora_import_template.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -339,6 +339,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -726,6 +741,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -810,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
@@ -5089,8 +5106,9 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5136,10 +5154,15 @@
       </c>
       <c r="F4" s="38" t="inlineStr">
         <is>
+          <t>Client Name</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="G4" s="38" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -5173,10 +5196,15 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
+          <t>Must match Clients sheet</t>
+        </is>
+      </c>
+      <c r="G5" s="42" t="inlineStr">
+        <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -5204,12 +5232,13 @@
         </is>
       </c>
       <c r="E6" s="39" t="inlineStr"/>
-      <c r="F6" s="39" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr"/>
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="G6" s="39" t="inlineStr"/>
+      <c r="H6" s="43" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
@@ -5237,12 +5266,13 @@
           <t>Website Redesign</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>Send to client</t>
         </is>
@@ -5267,7 +5297,8 @@
       </c>
       <c r="E8" s="39" t="inlineStr"/>
       <c r="F8" s="39" t="inlineStr"/>
-      <c r="G8" s="39" t="inlineStr"/>
+      <c r="G8" s="39" t="n"/>
+      <c r="H8" s="43" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="23" t="inlineStr"/>
@@ -5276,7 +5307,8 @@
       <c r="D9" s="23" t="inlineStr"/>
       <c r="E9" s="23" t="inlineStr"/>
       <c r="F9" s="23" t="inlineStr"/>
-      <c r="G9" s="23" t="inlineStr"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="39" t="inlineStr"/>
@@ -5285,7 +5317,8 @@
       <c r="D10" s="39" t="inlineStr"/>
       <c r="E10" s="39" t="inlineStr"/>
       <c r="F10" s="39" t="inlineStr"/>
-      <c r="G10" s="39" t="inlineStr"/>
+      <c r="G10" s="39" t="n"/>
+      <c r="H10" s="39" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="23" t="inlineStr"/>
@@ -5294,7 +5327,8 @@
       <c r="D11" s="23" t="inlineStr"/>
       <c r="E11" s="23" t="inlineStr"/>
       <c r="F11" s="23" t="inlineStr"/>
-      <c r="G11" s="23" t="inlineStr"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="39" t="inlineStr"/>
@@ -5303,7 +5337,8 @@
       <c r="D12" s="39" t="inlineStr"/>
       <c r="E12" s="39" t="inlineStr"/>
       <c r="F12" s="39" t="inlineStr"/>
-      <c r="G12" s="39" t="inlineStr"/>
+      <c r="G12" s="39" t="n"/>
+      <c r="H12" s="39" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
@@ -5312,7 +5347,8 @@
       <c r="D13" s="23" t="inlineStr"/>
       <c r="E13" s="23" t="inlineStr"/>
       <c r="F13" s="23" t="inlineStr"/>
-      <c r="G13" s="23" t="inlineStr"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="39" t="inlineStr"/>
@@ -5321,7 +5357,8 @@
       <c r="D14" s="39" t="inlineStr"/>
       <c r="E14" s="39" t="inlineStr"/>
       <c r="F14" s="39" t="inlineStr"/>
-      <c r="G14" s="39" t="inlineStr"/>
+      <c r="G14" s="39" t="n"/>
+      <c r="H14" s="39" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="23" t="inlineStr"/>
@@ -5330,7 +5367,8 @@
       <c r="D15" s="23" t="inlineStr"/>
       <c r="E15" s="23" t="inlineStr"/>
       <c r="F15" s="23" t="inlineStr"/>
-      <c r="G15" s="23" t="inlineStr"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="39" t="inlineStr"/>
@@ -5339,7 +5377,8 @@
       <c r="D16" s="39" t="inlineStr"/>
       <c r="E16" s="39" t="inlineStr"/>
       <c r="F16" s="39" t="inlineStr"/>
-      <c r="G16" s="39" t="inlineStr"/>
+      <c r="G16" s="39" t="n"/>
+      <c r="H16" s="39" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="23" t="inlineStr"/>
@@ -5348,7 +5387,8 @@
       <c r="D17" s="23" t="inlineStr"/>
       <c r="E17" s="23" t="inlineStr"/>
       <c r="F17" s="23" t="inlineStr"/>
-      <c r="G17" s="23" t="inlineStr"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="39" t="inlineStr"/>
@@ -5357,7 +5397,8 @@
       <c r="D18" s="39" t="inlineStr"/>
       <c r="E18" s="39" t="inlineStr"/>
       <c r="F18" s="39" t="inlineStr"/>
-      <c r="G18" s="39" t="inlineStr"/>
+      <c r="G18" s="39" t="n"/>
+      <c r="H18" s="39" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="23" t="inlineStr"/>
@@ -5366,7 +5407,8 @@
       <c r="D19" s="23" t="inlineStr"/>
       <c r="E19" s="23" t="inlineStr"/>
       <c r="F19" s="23" t="inlineStr"/>
-      <c r="G19" s="23" t="inlineStr"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="39" t="inlineStr"/>
@@ -5375,7 +5417,8 @@
       <c r="D20" s="39" t="inlineStr"/>
       <c r="E20" s="39" t="inlineStr"/>
       <c r="F20" s="39" t="inlineStr"/>
-      <c r="G20" s="39" t="inlineStr"/>
+      <c r="G20" s="39" t="n"/>
+      <c r="H20" s="39" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="23" t="inlineStr"/>
@@ -5384,7 +5427,8 @@
       <c r="D21" s="23" t="inlineStr"/>
       <c r="E21" s="23" t="inlineStr"/>
       <c r="F21" s="23" t="inlineStr"/>
-      <c r="G21" s="23" t="inlineStr"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="39" t="inlineStr"/>
@@ -5393,7 +5437,8 @@
       <c r="D22" s="39" t="inlineStr"/>
       <c r="E22" s="39" t="inlineStr"/>
       <c r="F22" s="39" t="inlineStr"/>
-      <c r="G22" s="39" t="inlineStr"/>
+      <c r="G22" s="39" t="n"/>
+      <c r="H22" s="39" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="23" t="inlineStr"/>
@@ -5402,7 +5447,8 @@
       <c r="D23" s="23" t="inlineStr"/>
       <c r="E23" s="23" t="inlineStr"/>
       <c r="F23" s="23" t="inlineStr"/>
-      <c r="G23" s="23" t="inlineStr"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="39" t="inlineStr"/>
@@ -5411,7 +5457,8 @@
       <c r="D24" s="39" t="inlineStr"/>
       <c r="E24" s="39" t="inlineStr"/>
       <c r="F24" s="39" t="inlineStr"/>
-      <c r="G24" s="39" t="inlineStr"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="23" t="inlineStr"/>
@@ -5420,7 +5467,8 @@
       <c r="D25" s="23" t="inlineStr"/>
       <c r="E25" s="23" t="inlineStr"/>
       <c r="F25" s="23" t="inlineStr"/>
-      <c r="G25" s="23" t="inlineStr"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="39" t="inlineStr"/>
@@ -5429,7 +5477,8 @@
       <c r="D26" s="39" t="inlineStr"/>
       <c r="E26" s="39" t="inlineStr"/>
       <c r="F26" s="39" t="inlineStr"/>
-      <c r="G26" s="39" t="inlineStr"/>
+      <c r="G26" s="39" t="n"/>
+      <c r="H26" s="39" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="23" t="inlineStr"/>
@@ -5438,7 +5487,8 @@
       <c r="D27" s="23" t="inlineStr"/>
       <c r="E27" s="23" t="inlineStr"/>
       <c r="F27" s="23" t="inlineStr"/>
-      <c r="G27" s="23" t="inlineStr"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="23" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="39" t="inlineStr"/>
@@ -5447,7 +5497,8 @@
       <c r="D28" s="39" t="inlineStr"/>
       <c r="E28" s="39" t="inlineStr"/>
       <c r="F28" s="39" t="inlineStr"/>
-      <c r="G28" s="39" t="inlineStr"/>
+      <c r="G28" s="39" t="n"/>
+      <c r="H28" s="39" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="23" t="inlineStr"/>
@@ -5456,7 +5507,8 @@
       <c r="D29" s="23" t="inlineStr"/>
       <c r="E29" s="23" t="inlineStr"/>
       <c r="F29" s="23" t="inlineStr"/>
-      <c r="G29" s="23" t="inlineStr"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="39" t="inlineStr"/>
@@ -5465,7 +5517,8 @@
       <c r="D30" s="39" t="inlineStr"/>
       <c r="E30" s="39" t="inlineStr"/>
       <c r="F30" s="39" t="inlineStr"/>
-      <c r="G30" s="39" t="inlineStr"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="23" t="inlineStr"/>
@@ -5474,7 +5527,8 @@
       <c r="D31" s="23" t="inlineStr"/>
       <c r="E31" s="23" t="inlineStr"/>
       <c r="F31" s="23" t="inlineStr"/>
-      <c r="G31" s="23" t="inlineStr"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="39" t="inlineStr"/>
@@ -5483,7 +5537,8 @@
       <c r="D32" s="39" t="inlineStr"/>
       <c r="E32" s="39" t="inlineStr"/>
       <c r="F32" s="39" t="inlineStr"/>
-      <c r="G32" s="39" t="inlineStr"/>
+      <c r="G32" s="39" t="n"/>
+      <c r="H32" s="39" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="23" t="inlineStr"/>
@@ -5492,7 +5547,8 @@
       <c r="D33" s="23" t="inlineStr"/>
       <c r="E33" s="23" t="inlineStr"/>
       <c r="F33" s="23" t="inlineStr"/>
-      <c r="G33" s="23" t="inlineStr"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="39" t="inlineStr"/>
@@ -5501,7 +5557,8 @@
       <c r="D34" s="39" t="inlineStr"/>
       <c r="E34" s="39" t="inlineStr"/>
       <c r="F34" s="39" t="inlineStr"/>
-      <c r="G34" s="39" t="inlineStr"/>
+      <c r="G34" s="39" t="n"/>
+      <c r="H34" s="39" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="23" t="inlineStr"/>
@@ -5510,7 +5567,8 @@
       <c r="D35" s="23" t="inlineStr"/>
       <c r="E35" s="23" t="inlineStr"/>
       <c r="F35" s="23" t="inlineStr"/>
-      <c r="G35" s="23" t="inlineStr"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="23" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="39" t="inlineStr"/>
@@ -5519,7 +5577,8 @@
       <c r="D36" s="39" t="inlineStr"/>
       <c r="E36" s="39" t="inlineStr"/>
       <c r="F36" s="39" t="inlineStr"/>
-      <c r="G36" s="39" t="inlineStr"/>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="23" t="inlineStr"/>
@@ -5528,7 +5587,8 @@
       <c r="D37" s="23" t="inlineStr"/>
       <c r="E37" s="23" t="inlineStr"/>
       <c r="F37" s="23" t="inlineStr"/>
-      <c r="G37" s="23" t="inlineStr"/>
+      <c r="G37" s="23" t="n"/>
+      <c r="H37" s="23" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="39" t="inlineStr"/>
@@ -5537,7 +5597,8 @@
       <c r="D38" s="39" t="inlineStr"/>
       <c r="E38" s="39" t="inlineStr"/>
       <c r="F38" s="39" t="inlineStr"/>
-      <c r="G38" s="39" t="inlineStr"/>
+      <c r="G38" s="39" t="n"/>
+      <c r="H38" s="39" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="23" t="inlineStr"/>
@@ -5546,7 +5607,8 @@
       <c r="D39" s="23" t="inlineStr"/>
       <c r="E39" s="23" t="inlineStr"/>
       <c r="F39" s="23" t="inlineStr"/>
-      <c r="G39" s="23" t="inlineStr"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="39" t="inlineStr"/>
@@ -5555,7 +5617,8 @@
       <c r="D40" s="39" t="inlineStr"/>
       <c r="E40" s="39" t="inlineStr"/>
       <c r="F40" s="39" t="inlineStr"/>
-      <c r="G40" s="39" t="inlineStr"/>
+      <c r="G40" s="39" t="n"/>
+      <c r="H40" s="39" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="23" t="inlineStr"/>
@@ -5564,7 +5627,8 @@
       <c r="D41" s="23" t="inlineStr"/>
       <c r="E41" s="23" t="inlineStr"/>
       <c r="F41" s="23" t="inlineStr"/>
-      <c r="G41" s="23" t="inlineStr"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="23" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="39" t="inlineStr"/>
@@ -5573,7 +5637,8 @@
       <c r="D42" s="39" t="inlineStr"/>
       <c r="E42" s="39" t="inlineStr"/>
       <c r="F42" s="39" t="inlineStr"/>
-      <c r="G42" s="39" t="inlineStr"/>
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="39" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="23" t="inlineStr"/>
@@ -5582,7 +5647,8 @@
       <c r="D43" s="23" t="inlineStr"/>
       <c r="E43" s="23" t="inlineStr"/>
       <c r="F43" s="23" t="inlineStr"/>
-      <c r="G43" s="23" t="inlineStr"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="39" t="inlineStr"/>
@@ -5591,7 +5657,8 @@
       <c r="D44" s="39" t="inlineStr"/>
       <c r="E44" s="39" t="inlineStr"/>
       <c r="F44" s="39" t="inlineStr"/>
-      <c r="G44" s="39" t="inlineStr"/>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="39" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="23" t="inlineStr"/>
@@ -5600,7 +5667,8 @@
       <c r="D45" s="23" t="inlineStr"/>
       <c r="E45" s="23" t="inlineStr"/>
       <c r="F45" s="23" t="inlineStr"/>
-      <c r="G45" s="23" t="inlineStr"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="23" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="39" t="inlineStr"/>
@@ -5609,7 +5677,8 @@
       <c r="D46" s="39" t="inlineStr"/>
       <c r="E46" s="39" t="inlineStr"/>
       <c r="F46" s="39" t="inlineStr"/>
-      <c r="G46" s="39" t="inlineStr"/>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="39" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="23" t="inlineStr"/>
@@ -5618,7 +5687,8 @@
       <c r="D47" s="23" t="inlineStr"/>
       <c r="E47" s="23" t="inlineStr"/>
       <c r="F47" s="23" t="inlineStr"/>
-      <c r="G47" s="23" t="inlineStr"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="23" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="39" t="inlineStr"/>
@@ -5627,7 +5697,8 @@
       <c r="D48" s="39" t="inlineStr"/>
       <c r="E48" s="39" t="inlineStr"/>
       <c r="F48" s="39" t="inlineStr"/>
-      <c r="G48" s="39" t="inlineStr"/>
+      <c r="G48" s="39" t="n"/>
+      <c r="H48" s="39" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="23" t="inlineStr"/>
@@ -5636,7 +5707,8 @@
       <c r="D49" s="23" t="inlineStr"/>
       <c r="E49" s="23" t="inlineStr"/>
       <c r="F49" s="23" t="inlineStr"/>
-      <c r="G49" s="23" t="inlineStr"/>
+      <c r="G49" s="23" t="n"/>
+      <c r="H49" s="23" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="39" t="inlineStr"/>
@@ -5645,7 +5717,8 @@
       <c r="D50" s="39" t="inlineStr"/>
       <c r="E50" s="39" t="inlineStr"/>
       <c r="F50" s="39" t="inlineStr"/>
-      <c r="G50" s="39" t="inlineStr"/>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="39" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="23" t="inlineStr"/>
@@ -5654,7 +5727,8 @@
       <c r="D51" s="23" t="inlineStr"/>
       <c r="E51" s="23" t="inlineStr"/>
       <c r="F51" s="23" t="inlineStr"/>
-      <c r="G51" s="23" t="inlineStr"/>
+      <c r="G51" s="23" t="n"/>
+      <c r="H51" s="23" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="39" t="inlineStr"/>
@@ -5663,7 +5737,8 @@
       <c r="D52" s="39" t="inlineStr"/>
       <c r="E52" s="39" t="inlineStr"/>
       <c r="F52" s="39" t="inlineStr"/>
-      <c r="G52" s="39" t="inlineStr"/>
+      <c r="G52" s="39" t="n"/>
+      <c r="H52" s="39" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="23" t="inlineStr"/>
@@ -5672,7 +5747,8 @@
       <c r="D53" s="23" t="inlineStr"/>
       <c r="E53" s="23" t="inlineStr"/>
       <c r="F53" s="23" t="inlineStr"/>
-      <c r="G53" s="23" t="inlineStr"/>
+      <c r="G53" s="23" t="n"/>
+      <c r="H53" s="23" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="39" t="inlineStr"/>
@@ -5681,7 +5757,8 @@
       <c r="D54" s="39" t="inlineStr"/>
       <c r="E54" s="39" t="inlineStr"/>
       <c r="F54" s="39" t="inlineStr"/>
-      <c r="G54" s="39" t="inlineStr"/>
+      <c r="G54" s="39" t="n"/>
+      <c r="H54" s="39" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="23" t="inlineStr"/>
@@ -5690,7 +5767,8 @@
       <c r="D55" s="23" t="inlineStr"/>
       <c r="E55" s="23" t="inlineStr"/>
       <c r="F55" s="23" t="inlineStr"/>
-      <c r="G55" s="23" t="inlineStr"/>
+      <c r="G55" s="23" t="n"/>
+      <c r="H55" s="23" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="39" t="inlineStr"/>
@@ -5699,7 +5777,8 @@
       <c r="D56" s="39" t="inlineStr"/>
       <c r="E56" s="39" t="inlineStr"/>
       <c r="F56" s="39" t="inlineStr"/>
-      <c r="G56" s="39" t="inlineStr"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="23" t="inlineStr"/>
@@ -5708,7 +5787,8 @@
       <c r="D57" s="23" t="inlineStr"/>
       <c r="E57" s="23" t="inlineStr"/>
       <c r="F57" s="23" t="inlineStr"/>
-      <c r="G57" s="23" t="inlineStr"/>
+      <c r="G57" s="23" t="n"/>
+      <c r="H57" s="23" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="39" t="inlineStr"/>
@@ -5717,7 +5797,8 @@
       <c r="D58" s="39" t="inlineStr"/>
       <c r="E58" s="39" t="inlineStr"/>
       <c r="F58" s="39" t="inlineStr"/>
-      <c r="G58" s="39" t="inlineStr"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="23" t="inlineStr"/>
@@ -5726,7 +5807,8 @@
       <c r="D59" s="23" t="inlineStr"/>
       <c r="E59" s="23" t="inlineStr"/>
       <c r="F59" s="23" t="inlineStr"/>
-      <c r="G59" s="23" t="inlineStr"/>
+      <c r="G59" s="23" t="n"/>
+      <c r="H59" s="23" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="39" t="inlineStr"/>
@@ -5735,7 +5817,8 @@
       <c r="D60" s="39" t="inlineStr"/>
       <c r="E60" s="39" t="inlineStr"/>
       <c r="F60" s="39" t="inlineStr"/>
-      <c r="G60" s="39" t="inlineStr"/>
+      <c r="G60" s="39" t="n"/>
+      <c r="H60" s="39" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="23" t="inlineStr"/>
@@ -5744,7 +5827,8 @@
       <c r="D61" s="23" t="inlineStr"/>
       <c r="E61" s="23" t="inlineStr"/>
       <c r="F61" s="23" t="inlineStr"/>
-      <c r="G61" s="23" t="inlineStr"/>
+      <c r="G61" s="23" t="n"/>
+      <c r="H61" s="23" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="39" t="inlineStr"/>
@@ -5753,7 +5837,8 @@
       <c r="D62" s="39" t="inlineStr"/>
       <c r="E62" s="39" t="inlineStr"/>
       <c r="F62" s="39" t="inlineStr"/>
-      <c r="G62" s="39" t="inlineStr"/>
+      <c r="G62" s="39" t="n"/>
+      <c r="H62" s="39" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="23" t="inlineStr"/>
@@ -5762,7 +5847,8 @@
       <c r="D63" s="23" t="inlineStr"/>
       <c r="E63" s="23" t="inlineStr"/>
       <c r="F63" s="23" t="inlineStr"/>
-      <c r="G63" s="23" t="inlineStr"/>
+      <c r="G63" s="23" t="n"/>
+      <c r="H63" s="23" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="39" t="inlineStr"/>
@@ -5771,7 +5857,8 @@
       <c r="D64" s="39" t="inlineStr"/>
       <c r="E64" s="39" t="inlineStr"/>
       <c r="F64" s="39" t="inlineStr"/>
-      <c r="G64" s="39" t="inlineStr"/>
+      <c r="G64" s="39" t="n"/>
+      <c r="H64" s="39" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="23" t="inlineStr"/>
@@ -5780,7 +5867,8 @@
       <c r="D65" s="23" t="inlineStr"/>
       <c r="E65" s="23" t="inlineStr"/>
       <c r="F65" s="23" t="inlineStr"/>
-      <c r="G65" s="23" t="inlineStr"/>
+      <c r="G65" s="23" t="n"/>
+      <c r="H65" s="23" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="39" t="inlineStr"/>
@@ -5789,7 +5877,8 @@
       <c r="D66" s="39" t="inlineStr"/>
       <c r="E66" s="39" t="inlineStr"/>
       <c r="F66" s="39" t="inlineStr"/>
-      <c r="G66" s="39" t="inlineStr"/>
+      <c r="G66" s="39" t="n"/>
+      <c r="H66" s="39" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="23" t="inlineStr"/>
@@ -5798,7 +5887,8 @@
       <c r="D67" s="23" t="inlineStr"/>
       <c r="E67" s="23" t="inlineStr"/>
       <c r="F67" s="23" t="inlineStr"/>
-      <c r="G67" s="23" t="inlineStr"/>
+      <c r="G67" s="23" t="n"/>
+      <c r="H67" s="23" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="39" t="inlineStr"/>
@@ -5807,7 +5897,8 @@
       <c r="D68" s="39" t="inlineStr"/>
       <c r="E68" s="39" t="inlineStr"/>
       <c r="F68" s="39" t="inlineStr"/>
-      <c r="G68" s="39" t="inlineStr"/>
+      <c r="G68" s="39" t="n"/>
+      <c r="H68" s="39" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="23" t="inlineStr"/>
@@ -5816,7 +5907,8 @@
       <c r="D69" s="23" t="inlineStr"/>
       <c r="E69" s="23" t="inlineStr"/>
       <c r="F69" s="23" t="inlineStr"/>
-      <c r="G69" s="23" t="inlineStr"/>
+      <c r="G69" s="23" t="n"/>
+      <c r="H69" s="23" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="39" t="inlineStr"/>
@@ -5825,7 +5917,8 @@
       <c r="D70" s="39" t="inlineStr"/>
       <c r="E70" s="39" t="inlineStr"/>
       <c r="F70" s="39" t="inlineStr"/>
-      <c r="G70" s="39" t="inlineStr"/>
+      <c r="G70" s="39" t="n"/>
+      <c r="H70" s="39" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="23" t="inlineStr"/>
@@ -5834,7 +5927,8 @@
       <c r="D71" s="23" t="inlineStr"/>
       <c r="E71" s="23" t="inlineStr"/>
       <c r="F71" s="23" t="inlineStr"/>
-      <c r="G71" s="23" t="inlineStr"/>
+      <c r="G71" s="23" t="n"/>
+      <c r="H71" s="23" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="39" t="inlineStr"/>
@@ -5843,7 +5937,8 @@
       <c r="D72" s="39" t="inlineStr"/>
       <c r="E72" s="39" t="inlineStr"/>
       <c r="F72" s="39" t="inlineStr"/>
-      <c r="G72" s="39" t="inlineStr"/>
+      <c r="G72" s="39" t="n"/>
+      <c r="H72" s="39" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="23" t="inlineStr"/>
@@ -5852,7 +5947,8 @@
       <c r="D73" s="23" t="inlineStr"/>
       <c r="E73" s="23" t="inlineStr"/>
       <c r="F73" s="23" t="inlineStr"/>
-      <c r="G73" s="23" t="inlineStr"/>
+      <c r="G73" s="23" t="n"/>
+      <c r="H73" s="23" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="39" t="inlineStr"/>
@@ -5861,7 +5957,8 @@
       <c r="D74" s="39" t="inlineStr"/>
       <c r="E74" s="39" t="inlineStr"/>
       <c r="F74" s="39" t="inlineStr"/>
-      <c r="G74" s="39" t="inlineStr"/>
+      <c r="G74" s="39" t="n"/>
+      <c r="H74" s="39" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="23" t="inlineStr"/>
@@ -5870,7 +5967,8 @@
       <c r="D75" s="23" t="inlineStr"/>
       <c r="E75" s="23" t="inlineStr"/>
       <c r="F75" s="23" t="inlineStr"/>
-      <c r="G75" s="23" t="inlineStr"/>
+      <c r="G75" s="23" t="n"/>
+      <c r="H75" s="23" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="39" t="inlineStr"/>
@@ -5879,7 +5977,8 @@
       <c r="D76" s="39" t="inlineStr"/>
       <c r="E76" s="39" t="inlineStr"/>
       <c r="F76" s="39" t="inlineStr"/>
-      <c r="G76" s="39" t="inlineStr"/>
+      <c r="G76" s="39" t="n"/>
+      <c r="H76" s="39" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="23" t="inlineStr"/>
@@ -5888,7 +5987,8 @@
       <c r="D77" s="23" t="inlineStr"/>
       <c r="E77" s="23" t="inlineStr"/>
       <c r="F77" s="23" t="inlineStr"/>
-      <c r="G77" s="23" t="inlineStr"/>
+      <c r="G77" s="23" t="n"/>
+      <c r="H77" s="23" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="39" t="inlineStr"/>
@@ -5897,7 +5997,8 @@
       <c r="D78" s="39" t="inlineStr"/>
       <c r="E78" s="39" t="inlineStr"/>
       <c r="F78" s="39" t="inlineStr"/>
-      <c r="G78" s="39" t="inlineStr"/>
+      <c r="G78" s="39" t="n"/>
+      <c r="H78" s="39" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="23" t="inlineStr"/>
@@ -5906,7 +6007,8 @@
       <c r="D79" s="23" t="inlineStr"/>
       <c r="E79" s="23" t="inlineStr"/>
       <c r="F79" s="23" t="inlineStr"/>
-      <c r="G79" s="23" t="inlineStr"/>
+      <c r="G79" s="23" t="n"/>
+      <c r="H79" s="23" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="39" t="inlineStr"/>
@@ -5915,7 +6017,8 @@
       <c r="D80" s="39" t="inlineStr"/>
       <c r="E80" s="39" t="inlineStr"/>
       <c r="F80" s="39" t="inlineStr"/>
-      <c r="G80" s="39" t="inlineStr"/>
+      <c r="G80" s="39" t="n"/>
+      <c r="H80" s="39" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="23" t="inlineStr"/>
@@ -5924,7 +6027,8 @@
       <c r="D81" s="23" t="inlineStr"/>
       <c r="E81" s="23" t="inlineStr"/>
       <c r="F81" s="23" t="inlineStr"/>
-      <c r="G81" s="23" t="inlineStr"/>
+      <c r="G81" s="23" t="n"/>
+      <c r="H81" s="23" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="39" t="inlineStr"/>
@@ -5933,7 +6037,8 @@
       <c r="D82" s="39" t="inlineStr"/>
       <c r="E82" s="39" t="inlineStr"/>
       <c r="F82" s="39" t="inlineStr"/>
-      <c r="G82" s="39" t="inlineStr"/>
+      <c r="G82" s="39" t="n"/>
+      <c r="H82" s="39" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="23" t="inlineStr"/>
@@ -5942,7 +6047,8 @@
       <c r="D83" s="23" t="inlineStr"/>
       <c r="E83" s="23" t="inlineStr"/>
       <c r="F83" s="23" t="inlineStr"/>
-      <c r="G83" s="23" t="inlineStr"/>
+      <c r="G83" s="23" t="n"/>
+      <c r="H83" s="23" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="39" t="inlineStr"/>
@@ -5951,7 +6057,8 @@
       <c r="D84" s="39" t="inlineStr"/>
       <c r="E84" s="39" t="inlineStr"/>
       <c r="F84" s="39" t="inlineStr"/>
-      <c r="G84" s="39" t="inlineStr"/>
+      <c r="G84" s="39" t="n"/>
+      <c r="H84" s="39" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="23" t="inlineStr"/>
@@ -5960,7 +6067,8 @@
       <c r="D85" s="23" t="inlineStr"/>
       <c r="E85" s="23" t="inlineStr"/>
       <c r="F85" s="23" t="inlineStr"/>
-      <c r="G85" s="23" t="inlineStr"/>
+      <c r="G85" s="23" t="n"/>
+      <c r="H85" s="23" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="39" t="inlineStr"/>
@@ -5969,7 +6077,8 @@
       <c r="D86" s="39" t="inlineStr"/>
       <c r="E86" s="39" t="inlineStr"/>
       <c r="F86" s="39" t="inlineStr"/>
-      <c r="G86" s="39" t="inlineStr"/>
+      <c r="G86" s="39" t="n"/>
+      <c r="H86" s="39" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="23" t="inlineStr"/>
@@ -5978,7 +6087,8 @@
       <c r="D87" s="23" t="inlineStr"/>
       <c r="E87" s="23" t="inlineStr"/>
       <c r="F87" s="23" t="inlineStr"/>
-      <c r="G87" s="23" t="inlineStr"/>
+      <c r="G87" s="23" t="n"/>
+      <c r="H87" s="23" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="39" t="inlineStr"/>
@@ -5987,7 +6097,8 @@
       <c r="D88" s="39" t="inlineStr"/>
       <c r="E88" s="39" t="inlineStr"/>
       <c r="F88" s="39" t="inlineStr"/>
-      <c r="G88" s="39" t="inlineStr"/>
+      <c r="G88" s="39" t="n"/>
+      <c r="H88" s="39" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="23" t="inlineStr"/>
@@ -5996,7 +6107,8 @@
       <c r="D89" s="23" t="inlineStr"/>
       <c r="E89" s="23" t="inlineStr"/>
       <c r="F89" s="23" t="inlineStr"/>
-      <c r="G89" s="23" t="inlineStr"/>
+      <c r="G89" s="23" t="n"/>
+      <c r="H89" s="23" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="39" t="inlineStr"/>
@@ -6005,7 +6117,8 @@
       <c r="D90" s="39" t="inlineStr"/>
       <c r="E90" s="39" t="inlineStr"/>
       <c r="F90" s="39" t="inlineStr"/>
-      <c r="G90" s="39" t="inlineStr"/>
+      <c r="G90" s="39" t="n"/>
+      <c r="H90" s="39" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="23" t="inlineStr"/>
@@ -6014,7 +6127,8 @@
       <c r="D91" s="23" t="inlineStr"/>
       <c r="E91" s="23" t="inlineStr"/>
       <c r="F91" s="23" t="inlineStr"/>
-      <c r="G91" s="23" t="inlineStr"/>
+      <c r="G91" s="23" t="n"/>
+      <c r="H91" s="23" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="39" t="inlineStr"/>
@@ -6023,7 +6137,8 @@
       <c r="D92" s="39" t="inlineStr"/>
       <c r="E92" s="39" t="inlineStr"/>
       <c r="F92" s="39" t="inlineStr"/>
-      <c r="G92" s="39" t="inlineStr"/>
+      <c r="G92" s="39" t="n"/>
+      <c r="H92" s="39" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="23" t="inlineStr"/>
@@ -6032,7 +6147,8 @@
       <c r="D93" s="23" t="inlineStr"/>
       <c r="E93" s="23" t="inlineStr"/>
       <c r="F93" s="23" t="inlineStr"/>
-      <c r="G93" s="23" t="inlineStr"/>
+      <c r="G93" s="23" t="n"/>
+      <c r="H93" s="23" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="39" t="inlineStr"/>
@@ -6041,7 +6157,8 @@
       <c r="D94" s="39" t="inlineStr"/>
       <c r="E94" s="39" t="inlineStr"/>
       <c r="F94" s="39" t="inlineStr"/>
-      <c r="G94" s="39" t="inlineStr"/>
+      <c r="G94" s="39" t="n"/>
+      <c r="H94" s="39" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="23" t="inlineStr"/>
@@ -6050,7 +6167,8 @@
       <c r="D95" s="23" t="inlineStr"/>
       <c r="E95" s="23" t="inlineStr"/>
       <c r="F95" s="23" t="inlineStr"/>
-      <c r="G95" s="23" t="inlineStr"/>
+      <c r="G95" s="23" t="n"/>
+      <c r="H95" s="23" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="39" t="inlineStr"/>
@@ -6059,7 +6177,8 @@
       <c r="D96" s="39" t="inlineStr"/>
       <c r="E96" s="39" t="inlineStr"/>
       <c r="F96" s="39" t="inlineStr"/>
-      <c r="G96" s="39" t="inlineStr"/>
+      <c r="G96" s="39" t="n"/>
+      <c r="H96" s="39" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="23" t="inlineStr"/>
@@ -6068,7 +6187,8 @@
       <c r="D97" s="23" t="inlineStr"/>
       <c r="E97" s="23" t="inlineStr"/>
       <c r="F97" s="23" t="inlineStr"/>
-      <c r="G97" s="23" t="inlineStr"/>
+      <c r="G97" s="23" t="n"/>
+      <c r="H97" s="23" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="39" t="inlineStr"/>
@@ -6077,7 +6197,8 @@
       <c r="D98" s="39" t="inlineStr"/>
       <c r="E98" s="39" t="inlineStr"/>
       <c r="F98" s="39" t="inlineStr"/>
-      <c r="G98" s="39" t="inlineStr"/>
+      <c r="G98" s="39" t="n"/>
+      <c r="H98" s="39" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="23" t="inlineStr"/>
@@ -6086,7 +6207,8 @@
       <c r="D99" s="23" t="inlineStr"/>
       <c r="E99" s="23" t="inlineStr"/>
       <c r="F99" s="23" t="inlineStr"/>
-      <c r="G99" s="23" t="inlineStr"/>
+      <c r="G99" s="23" t="n"/>
+      <c r="H99" s="23" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="39" t="inlineStr"/>
@@ -6095,7 +6217,8 @@
       <c r="D100" s="39" t="inlineStr"/>
       <c r="E100" s="39" t="inlineStr"/>
       <c r="F100" s="39" t="inlineStr"/>
-      <c r="G100" s="39" t="inlineStr"/>
+      <c r="G100" s="39" t="n"/>
+      <c r="H100" s="39" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="23" t="inlineStr"/>
@@ -6104,7 +6227,8 @@
       <c r="D101" s="23" t="inlineStr"/>
       <c r="E101" s="23" t="inlineStr"/>
       <c r="F101" s="23" t="inlineStr"/>
-      <c r="G101" s="23" t="inlineStr"/>
+      <c r="G101" s="23" t="n"/>
+      <c r="H101" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/templates/planora_import_template.xlsx
+++ b/public/templates/planora_import_template.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✅ Tasks" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📥 One-Time Tasks" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔁 Recurring Tasks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏛️ CA Compliance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +108,42 @@
       <color rgb="FFEA580C"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00795548"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001565C0"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005D4037"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -200,8 +235,113 @@
         <fgColor rgb="FFD97706"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D3349"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B5E20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D47A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A148C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF360C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00006064"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0037474F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E65100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00880E4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00263238"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -223,11 +363,25 @@
         <color rgb="FFE2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -355,6 +509,117 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -741,7 +1006,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -826,7 +1090,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
@@ -4072,6 +4335,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4125,6 +4389,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="H4" s="45" t="inlineStr">
+        <is>
+          <t>Compliance Task Type</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
@@ -4160,6 +4429,11 @@
       <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="46" t="inlineStr">
+        <is>
+          <t>e.g. GSTR 3B (Monthly)  [optional — auto-fills subtasks]</t>
         </is>
       </c>
     </row>
@@ -6237,4 +6511,1128 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>🏛️ CA Compliance Tasks — Import Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>HOW TO USE: Fill Client Name + Assignee Email + Due Date. The Compliance Task Type auto-fills subtasks (document names). Leave rows blank to skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="49" t="inlineStr">
+        <is>
+          <t>Compliance Task Type *</t>
+        </is>
+      </c>
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>Client Name *</t>
+        </is>
+      </c>
+      <c r="C3" s="49" t="inlineStr">
+        <is>
+          <t>Assignee Email</t>
+        </is>
+      </c>
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>Due Date
+(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr">
+        <is>
+          <t>Priority
+(high/medium/low)</t>
+        </is>
+      </c>
+      <c r="F3" s="49" t="inlineStr">
+        <is>
+          <t>Frequency
+(blank=one-time)</t>
+        </is>
+      </c>
+      <c r="G3" s="49" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>GSTR 3B (Monthly)</t>
+        </is>
+      </c>
+      <c r="B4" s="50" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="C4" s="50" t="inlineStr">
+        <is>
+          <t>sachit@sngadvisers.com</t>
+        </is>
+      </c>
+      <c r="D4" s="50" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E4" s="50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F4" s="50" t="inlineStr"/>
+      <c r="G4" s="50" t="inlineStr">
+        <is>
+          <t>March filing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>── REFERENCE: All available compliance task types (copy the exact text into Column A above) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>GST R1 - IFF/ R1 Quaterly (QRMP)</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="55" t="n"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>Quaterly Only GST R1 - IFF/ R1 (QRMP)</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="55" t="n"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>GST 3B (QRMP North India)</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="55" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 1 (Monthly)</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="55" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 3B (Monthly)</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
+      <c r="G12" s="55" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 9 (Annual Return)</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
+      <c r="G13" s="55" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 9C (GST Audit - &gt;5cr)</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Signed Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="55" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>GSTR CMP 08 (Quaterly)</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="55" t="n"/>
+      <c r="G15" s="55" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 4 for Composition (Annual)</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+      <c r="F16" s="55" t="n"/>
+      <c r="G16" s="55" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>GSTR 2B (Reconciliation)</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="55" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>LUT for Export (GST)</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>Confirmation Screenshot</t>
+        </is>
+      </c>
+      <c r="C18" s="54" t="inlineStr"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
+      <c r="G18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TDS / TCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>TDS (26Q Challan)</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr"/>
+      <c r="D20" s="59" t="n"/>
+      <c r="E20" s="59" t="n"/>
+      <c r="F20" s="59" t="n"/>
+      <c r="G20" s="59" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="57" t="inlineStr">
+        <is>
+          <t>TDS (26Q Return)</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="inlineStr"/>
+      <c r="D21" s="59" t="n"/>
+      <c r="E21" s="59" t="n"/>
+      <c r="F21" s="59" t="n"/>
+      <c r="G21" s="59" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>TDS (24Q Challan)</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr"/>
+      <c r="D22" s="59" t="n"/>
+      <c r="E22" s="59" t="n"/>
+      <c r="F22" s="59" t="n"/>
+      <c r="G22" s="59" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="57" t="inlineStr">
+        <is>
+          <t>TDS (24Q Return)</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="inlineStr"/>
+      <c r="D23" s="59" t="n"/>
+      <c r="E23" s="59" t="n"/>
+      <c r="F23" s="59" t="n"/>
+      <c r="G23" s="59" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="57" t="inlineStr">
+        <is>
+          <t>TDS (27EQ Challan)</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr"/>
+      <c r="D24" s="59" t="n"/>
+      <c r="E24" s="59" t="n"/>
+      <c r="F24" s="59" t="n"/>
+      <c r="G24" s="59" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="57" t="inlineStr">
+        <is>
+          <t>TDS (27EQ Return)</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="inlineStr"/>
+      <c r="D25" s="59" t="n"/>
+      <c r="E25" s="59" t="n"/>
+      <c r="F25" s="59" t="n"/>
+      <c r="G25" s="59" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>TDS on Rent (Individual/Salary)</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr"/>
+      <c r="D26" s="59" t="n"/>
+      <c r="E26" s="59" t="n"/>
+      <c r="F26" s="59" t="n"/>
+      <c r="G26" s="59" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="57" t="inlineStr">
+        <is>
+          <t>Issue of Form 16A (NON Sal)</t>
+        </is>
+      </c>
+      <c r="B27" s="58" t="inlineStr">
+        <is>
+          <t>Forms Issued</t>
+        </is>
+      </c>
+      <c r="C27" s="58" t="inlineStr"/>
+      <c r="D27" s="59" t="n"/>
+      <c r="E27" s="59" t="n"/>
+      <c r="F27" s="59" t="n"/>
+      <c r="G27" s="59" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="57" t="inlineStr">
+        <is>
+          <t>Issue of Form 16 (Sal)</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="inlineStr">
+        <is>
+          <t>Forms Issued</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr"/>
+      <c r="D28" s="59" t="n"/>
+      <c r="E28" s="59" t="n"/>
+      <c r="F28" s="59" t="n"/>
+      <c r="G28" s="59" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INCOME TAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>Income Tax (Advance Tax)</t>
+        </is>
+      </c>
+      <c r="B30" s="62" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C30" s="62" t="inlineStr"/>
+      <c r="D30" s="63" t="n"/>
+      <c r="E30" s="63" t="n"/>
+      <c r="F30" s="63" t="n"/>
+      <c r="G30" s="63" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="61" t="inlineStr">
+        <is>
+          <t>ITR (Individual)</t>
+        </is>
+      </c>
+      <c r="B31" s="62" t="inlineStr">
+        <is>
+          <t>Folder of Documents received from Client</t>
+        </is>
+      </c>
+      <c r="C31" s="62" t="inlineStr">
+        <is>
+          <t>Final Computation after return filing</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="n"/>
+      <c r="E31" s="63" t="n"/>
+      <c r="F31" s="63" t="n"/>
+      <c r="G31" s="63" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>ITR (with Audit)</t>
+        </is>
+      </c>
+      <c r="B32" s="62" t="inlineStr">
+        <is>
+          <t>Folder of Documents received from Client</t>
+        </is>
+      </c>
+      <c r="C32" s="62" t="inlineStr">
+        <is>
+          <t>Final Computation after return filing</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="n"/>
+      <c r="E32" s="63" t="n"/>
+      <c r="F32" s="63" t="n"/>
+      <c r="G32" s="63" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="61" t="inlineStr">
+        <is>
+          <t>ITR (Unaudited)</t>
+        </is>
+      </c>
+      <c r="B33" s="62" t="inlineStr">
+        <is>
+          <t>Final Excel Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C33" s="62" t="inlineStr">
+        <is>
+          <t>Signed Copy of Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="n"/>
+      <c r="E33" s="63" t="n"/>
+      <c r="F33" s="63" t="n"/>
+      <c r="G33" s="63" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="61" t="inlineStr">
+        <is>
+          <t>ITR (NGO audit)</t>
+        </is>
+      </c>
+      <c r="B34" s="62" t="inlineStr">
+        <is>
+          <t>Folder of Documents received from Client</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="inlineStr">
+        <is>
+          <t>Final Computation after return filing</t>
+        </is>
+      </c>
+      <c r="D34" s="63" t="n"/>
+      <c r="E34" s="63" t="n"/>
+      <c r="F34" s="63" t="n"/>
+      <c r="G34" s="63" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="61" t="inlineStr">
+        <is>
+          <t>Form 10B (Tax Audit)</t>
+        </is>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>Final Excel Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C35" s="62" t="inlineStr">
+        <is>
+          <t>Signed Copy of Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="n"/>
+      <c r="E35" s="63" t="n"/>
+      <c r="F35" s="63" t="n"/>
+      <c r="G35" s="63" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROC / COMPANY LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="65" t="inlineStr">
+        <is>
+          <t>ROC for LLP (Form 11)</t>
+        </is>
+      </c>
+      <c r="B37" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C37" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D37" s="67" t="n"/>
+      <c r="E37" s="67" t="n"/>
+      <c r="F37" s="67" t="n"/>
+      <c r="G37" s="67" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t>ROC (INC-22A)</t>
+        </is>
+      </c>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C38" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="n"/>
+      <c r="E38" s="67" t="n"/>
+      <c r="F38" s="67" t="n"/>
+      <c r="G38" s="67" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="65" t="inlineStr">
+        <is>
+          <t>ROC (DIR-3 KYC)</t>
+        </is>
+      </c>
+      <c r="B39" s="66" t="inlineStr">
+        <is>
+          <t>Confirmation Screenshot</t>
+        </is>
+      </c>
+      <c r="C39" s="66" t="inlineStr"/>
+      <c r="D39" s="67" t="n"/>
+      <c r="E39" s="67" t="n"/>
+      <c r="F39" s="67" t="n"/>
+      <c r="G39" s="67" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="65" t="inlineStr">
+        <is>
+          <t>ROC (Form ADT-1)</t>
+        </is>
+      </c>
+      <c r="B40" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C40" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="n"/>
+      <c r="E40" s="67" t="n"/>
+      <c r="F40" s="67" t="n"/>
+      <c r="G40" s="67" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="65" t="inlineStr">
+        <is>
+          <t>ROC (DPT-3)</t>
+        </is>
+      </c>
+      <c r="B41" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C41" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="n"/>
+      <c r="E41" s="67" t="n"/>
+      <c r="F41" s="67" t="n"/>
+      <c r="G41" s="67" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="65" t="inlineStr">
+        <is>
+          <t>ROC for LLP (Form 8)</t>
+        </is>
+      </c>
+      <c r="B42" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C42" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D42" s="67" t="n"/>
+      <c r="E42" s="67" t="n"/>
+      <c r="F42" s="67" t="n"/>
+      <c r="G42" s="67" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="65" t="inlineStr">
+        <is>
+          <t>ROC (AOC-4) - 30 days of AGM</t>
+        </is>
+      </c>
+      <c r="B43" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C43" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D43" s="67" t="n"/>
+      <c r="E43" s="67" t="n"/>
+      <c r="F43" s="67" t="n"/>
+      <c r="G43" s="67" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="65" t="inlineStr">
+        <is>
+          <t>ROC (MGT-7) - 60 days of AGM</t>
+        </is>
+      </c>
+      <c r="B44" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C44" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="n"/>
+      <c r="E44" s="67" t="n"/>
+      <c r="F44" s="67" t="n"/>
+      <c r="G44" s="67" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="65" t="inlineStr">
+        <is>
+          <t>INC 20A (120 days from Inc)</t>
+        </is>
+      </c>
+      <c r="B45" s="66" t="inlineStr">
+        <is>
+          <t>Form Signed_Filed</t>
+        </is>
+      </c>
+      <c r="C45" s="66" t="inlineStr">
+        <is>
+          <t>Challan Copy</t>
+        </is>
+      </c>
+      <c r="D45" s="67" t="n"/>
+      <c r="E45" s="67" t="n"/>
+      <c r="F45" s="67" t="n"/>
+      <c r="G45" s="67" t="n"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ACCOUNTING &amp; MIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="69" t="inlineStr">
+        <is>
+          <t>Accounting (Monthly)</t>
+        </is>
+      </c>
+      <c r="B47" s="70" t="inlineStr">
+        <is>
+          <t>Tally Data</t>
+        </is>
+      </c>
+      <c r="C47" s="70" t="inlineStr"/>
+      <c r="D47" s="71" t="n"/>
+      <c r="E47" s="71" t="n"/>
+      <c r="F47" s="71" t="n"/>
+      <c r="G47" s="71" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="69" t="inlineStr">
+        <is>
+          <t>Accounting (Quaterly)</t>
+        </is>
+      </c>
+      <c r="B48" s="70" t="inlineStr">
+        <is>
+          <t>Tally Data</t>
+        </is>
+      </c>
+      <c r="C48" s="70" t="inlineStr"/>
+      <c r="D48" s="71" t="n"/>
+      <c r="E48" s="71" t="n"/>
+      <c r="F48" s="71" t="n"/>
+      <c r="G48" s="71" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="69" t="inlineStr">
+        <is>
+          <t>Balance Sheet (Unaudited)</t>
+        </is>
+      </c>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>Final Excel Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C49" s="70" t="inlineStr">
+        <is>
+          <t>Signed Copy of Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D49" s="71" t="n"/>
+      <c r="E49" s="71" t="n"/>
+      <c r="F49" s="71" t="n"/>
+      <c r="G49" s="71" t="n"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AUDIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="73" t="inlineStr">
+        <is>
+          <t>TAX Audit</t>
+        </is>
+      </c>
+      <c r="B51" s="74" t="inlineStr">
+        <is>
+          <t>Final Excel Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C51" s="74" t="inlineStr">
+        <is>
+          <t>Signed Copy of Balance Sheet with Tax Audit Report</t>
+        </is>
+      </c>
+      <c r="D51" s="75" t="n"/>
+      <c r="E51" s="75" t="n"/>
+      <c r="F51" s="75" t="n"/>
+      <c r="G51" s="75" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="73" t="inlineStr">
+        <is>
+          <t>Statutory Audit</t>
+        </is>
+      </c>
+      <c r="B52" s="74" t="inlineStr">
+        <is>
+          <t>Final Excel Balance Sheet</t>
+        </is>
+      </c>
+      <c r="C52" s="74" t="inlineStr">
+        <is>
+          <t>Signed Copy of Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D52" s="75" t="n"/>
+      <c r="E52" s="75" t="n"/>
+      <c r="F52" s="75" t="n"/>
+      <c r="G52" s="75" t="n"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="73" t="inlineStr">
+        <is>
+          <t>Concurrent Audit PSB (Monthly)</t>
+        </is>
+      </c>
+      <c r="B53" s="74" t="inlineStr">
+        <is>
+          <t>FRC</t>
+        </is>
+      </c>
+      <c r="C53" s="74" t="inlineStr">
+        <is>
+          <t>ScreenShot of Report Submitted</t>
+        </is>
+      </c>
+      <c r="D53" s="75" t="n"/>
+      <c r="E53" s="75" t="n"/>
+      <c r="F53" s="75" t="n"/>
+      <c r="G53" s="75" t="n"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="73" t="inlineStr">
+        <is>
+          <t>Concurrent Audit PSB (Quarterly)</t>
+        </is>
+      </c>
+      <c r="B54" s="74" t="inlineStr">
+        <is>
+          <t>FRC</t>
+        </is>
+      </c>
+      <c r="C54" s="74" t="inlineStr">
+        <is>
+          <t>ScreenShot of Report Submitted</t>
+        </is>
+      </c>
+      <c r="D54" s="75" t="n"/>
+      <c r="E54" s="75" t="n"/>
+      <c r="F54" s="75" t="n"/>
+      <c r="G54" s="75" t="n"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LABOUR &amp; PAYROLL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="77" t="inlineStr">
+        <is>
+          <t>ESI (Challan)</t>
+        </is>
+      </c>
+      <c r="B56" s="78" t="inlineStr">
+        <is>
+          <t>Confirmation Screenshot</t>
+        </is>
+      </c>
+      <c r="C56" s="78" t="inlineStr"/>
+      <c r="D56" s="79" t="n"/>
+      <c r="E56" s="79" t="n"/>
+      <c r="F56" s="79" t="n"/>
+      <c r="G56" s="79" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="77" t="inlineStr">
+        <is>
+          <t>ESI (Return)</t>
+        </is>
+      </c>
+      <c r="B57" s="78" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C57" s="78" t="inlineStr"/>
+      <c r="D57" s="79" t="n"/>
+      <c r="E57" s="79" t="n"/>
+      <c r="F57" s="79" t="n"/>
+      <c r="G57" s="79" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="77" t="inlineStr">
+        <is>
+          <t>PF (Challan)</t>
+        </is>
+      </c>
+      <c r="B58" s="78" t="inlineStr">
+        <is>
+          <t>Confirmation Screenshot</t>
+        </is>
+      </c>
+      <c r="C58" s="78" t="inlineStr"/>
+      <c r="D58" s="79" t="n"/>
+      <c r="E58" s="79" t="n"/>
+      <c r="F58" s="79" t="n"/>
+      <c r="G58" s="79" t="n"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="77" t="inlineStr">
+        <is>
+          <t>PF (Return)</t>
+        </is>
+      </c>
+      <c r="B59" s="78" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C59" s="78" t="inlineStr"/>
+      <c r="D59" s="79" t="n"/>
+      <c r="E59" s="79" t="n"/>
+      <c r="F59" s="79" t="n"/>
+      <c r="G59" s="79" t="n"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NGO / FCRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="81" t="inlineStr">
+        <is>
+          <t>FCRA (Quaterly)</t>
+        </is>
+      </c>
+      <c r="B61" s="82" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C61" s="82" t="inlineStr"/>
+      <c r="D61" s="83" t="n"/>
+      <c r="E61" s="83" t="n"/>
+      <c r="F61" s="83" t="n"/>
+      <c r="G61" s="83" t="n"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="81" t="inlineStr">
+        <is>
+          <t>FCRA (Annual Return)</t>
+        </is>
+      </c>
+      <c r="B62" s="82" t="inlineStr">
+        <is>
+          <t>Computation</t>
+        </is>
+      </c>
+      <c r="C62" s="82" t="inlineStr"/>
+      <c r="D62" s="83" t="n"/>
+      <c r="E62" s="83" t="n"/>
+      <c r="F62" s="83" t="n"/>
+      <c r="G62" s="83" t="n"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="81" t="inlineStr">
+        <is>
+          <t>Form 10BD (NGO)</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="inlineStr">
+        <is>
+          <t>File received from Client</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>Forms Issued</t>
+        </is>
+      </c>
+      <c r="D63" s="83" t="n"/>
+      <c r="E63" s="83" t="n"/>
+      <c r="F63" s="83" t="n"/>
+      <c r="G63" s="83" t="n"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OTHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="85" t="inlineStr">
+        <is>
+          <t>IEC Code (Renewal for Export)</t>
+        </is>
+      </c>
+      <c r="B65" s="86" t="inlineStr">
+        <is>
+          <t>Confirmation Screenshot</t>
+        </is>
+      </c>
+      <c r="C65" s="86" t="inlineStr"/>
+      <c r="D65" s="87" t="n"/>
+      <c r="E65" s="87" t="n"/>
+      <c r="F65" s="87" t="n"/>
+      <c r="G65" s="87" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>